--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -14560,7 +14560,7 @@
         <v>83</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>258</v>
+        <v>158</v>
       </c>
       <c r="Y100" t="s" s="2">
         <v>677</v>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -446,7 +446,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -466,7 +466,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>French profiling of the FHIR Vital Sign Heart Rate Profile.
+    <t>French profile for the FHIR Vital Sign Heart Rate Profile.
 Profilage français du profil Vital Signs Heart rate</t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -660,7 +660,8 @@
     <t>FR Core Observation Level Of Exertion Extension</t>
   </si>
   <si>
-    <t>French extension defined in the context of the Vital Signs Resprate profile. This extension is used to define the level of exertion ( at rest, during exertion, post exertion) during the respiratory rate measure | Extension française définie dans le contexte du profil Vital Signs Resprate. Cette extension permet de préciser le niveau d'exercice du patient durant la mesure de la fréquence respiratoire (au repos, pendant l'effort, après l'effort)</t>
+    <t>Extension française définie dans le contexte du profil Vital Signs Resprate. Cette extension permet de préciser le niveau d'exercice du patient durant la mesure de la fréquence respiratoire (au repos, pendant l'effort, après l'effort).
+French extension defined in the context of the Vital Signs Resprate profile. This extension is used to define the level of exertion ( at rest, during exertion, post exertion) during the respiratory rate measure</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -680,7 +681,8 @@
     <t>FR Core Observation Body Position Ext Extension</t>
   </si>
   <si>
-    <t>CIMI extension (in FHIR R4) defined in the context of the Respiratory Rate profile. This extension is used to specify the body position during the respiratory rate observation | Extension CIMI (upgardée en FHIR R4) définie dans le contexte du profil Respiratory rate. Cette extension permet de préciser la position du corps lors de la mesure de la fréquence respiratoire.</t>
+    <t>Extension CIMI (upgardée en FHIR R4) définie dans le contexte du profil Respiratory rate. Cette extension permet de préciser la position du corps lors de la mesure de la fréquence respiratoire.
+CIMI extension (in FHIR R4) defined in the context of the Respiratory Rate profile. This extension is used to specify the body position during the respiratory rate observation</t>
   </si>
   <si>
     <t>Observation.extension:supportingInfo</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$95</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3979" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3675" uniqueCount="668">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -691,7 +691,7 @@
     <t>supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {workflow-supportingInfo}
+    <t xml:space="preserve">Extension {workflow-supportingInfo|5.2.0}
 </t>
   </si>
   <si>
@@ -1685,7 +1685,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/hspc/ValueSet/heartRateMeasBodyLocationPrecoordVS</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-heartrate-body-location</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1700,21 +1700,6 @@
     <t>718497002 |Inherent location|</t>
   </si>
   <si>
-    <t>Observation.bodySite.id</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.extension</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.coding</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-heart-rate-body-position</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.text</t>
-  </si>
-  <si>
     <t>Observation.method</t>
   </si>
   <si>
@@ -1733,28 +1718,13 @@
     <t>Methods for heartrate observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/hspc/ValueSet/heartRateMeasMethodVS</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-heartrate-measurement-method</t>
   </si>
   <si>
     <t>OBX-17</t>
   </si>
   <si>
     <t>methodCode</t>
-  </si>
-  <si>
-    <t>Observation.method.id</t>
-  </si>
-  <si>
-    <t>Observation.method.extension</t>
-  </si>
-  <si>
-    <t>Observation.method.coding</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-heart-rate-method</t>
-  </si>
-  <si>
-    <t>Observation.method.text</t>
   </si>
   <si>
     <t>Observation.specimen</t>
@@ -2456,7 +2426,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP103"/>
+  <dimension ref="A1:AP95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.81640625" customWidth="true" bestFit="true"/>
@@ -2484,7 +2454,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.3359375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.5078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -11088,16 +11058,20 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>108</v>
+        <v>263</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>109</v>
+        <v>542</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
       </c>
@@ -11121,13 +11095,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>83</v>
+        <v>546</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>83</v>
+        <v>547</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -11145,7 +11119,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>111</v>
+        <v>541</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11157,7 +11131,7 @@
         <v>83</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>83</v>
@@ -11166,10 +11140,10 @@
         <v>83</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>83</v>
+        <v>548</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>112</v>
+        <v>549</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -11180,21 +11154,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>83</v>
@@ -11206,16 +11180,16 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>115</v>
+        <v>551</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>116</v>
+        <v>552</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>117</v>
+        <v>553</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>118</v>
+        <v>554</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11253,57 +11227,57 @@
         <v>83</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>122</v>
+        <v>550</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>83</v>
+        <v>555</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>83</v>
+        <v>556</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>112</v>
+        <v>557</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>83</v>
+        <v>558</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>543</v>
+        <v>559</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>543</v>
+        <v>559</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11314,7 +11288,7 @@
         <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>83</v>
@@ -11323,23 +11297,21 @@
         <v>83</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>152</v>
+        <v>560</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>281</v>
+        <v>561</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>282</v>
+        <v>562</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>83</v>
       </c>
@@ -11363,11 +11335,13 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y74" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z74" t="s" s="2">
-        <v>544</v>
+        <v>83</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11385,13 +11359,13 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>285</v>
+        <v>559</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>83</v>
@@ -11403,27 +11377,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>83</v>
+        <v>564</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>286</v>
+        <v>565</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>287</v>
+        <v>566</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>83</v>
+        <v>567</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>545</v>
+        <v>568</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>545</v>
+        <v>568</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11434,7 +11408,7 @@
         <v>81</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>83</v>
@@ -11443,22 +11417,22 @@
         <v>83</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>108</v>
+        <v>569</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>339</v>
+        <v>570</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>340</v>
+        <v>571</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>341</v>
+        <v>572</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>342</v>
+        <v>573</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11507,19 +11481,19 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>343</v>
+        <v>568</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>106</v>
+        <v>574</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>83</v>
@@ -11528,10 +11502,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>344</v>
+        <v>575</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>345</v>
+        <v>576</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11542,10 +11516,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>546</v>
+        <v>577</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>546</v>
+        <v>577</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11568,20 +11542,16 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>263</v>
+        <v>108</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>547</v>
+        <v>109</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>550</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>83</v>
       </c>
@@ -11605,13 +11575,13 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>551</v>
+        <v>83</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>552</v>
+        <v>83</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -11629,7 +11599,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>546</v>
+        <v>111</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11641,7 +11611,7 @@
         <v>83</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>83</v>
@@ -11650,10 +11620,10 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>553</v>
+        <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>554</v>
+        <v>112</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11664,21 +11634,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>555</v>
+        <v>578</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>555</v>
+        <v>578</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>83</v>
@@ -11690,15 +11660,17 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11747,19 +11719,19 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>83</v>
@@ -11782,14 +11754,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>556</v>
+        <v>579</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>556</v>
+        <v>579</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>114</v>
+        <v>580</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11802,24 +11774,26 @@
         <v>83</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>115</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>116</v>
+        <v>581</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>117</v>
+        <v>582</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="O78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
       </c>
@@ -11855,19 +11829,19 @@
         <v>83</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>122</v>
+        <v>583</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11891,7 +11865,7 @@
         <v>83</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11902,10 +11876,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>557</v>
+        <v>584</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>557</v>
+        <v>584</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11916,7 +11890,7 @@
         <v>81</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>83</v>
@@ -11925,23 +11899,19 @@
         <v>83</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>152</v>
+        <v>585</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>281</v>
+        <v>586</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>83</v>
       </c>
@@ -11965,11 +11935,13 @@
         <v>83</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>558</v>
+        <v>83</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>83</v>
@@ -11987,16 +11959,16 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>285</v>
+        <v>584</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>83</v>
+        <v>588</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>106</v>
@@ -12008,10 +11980,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>286</v>
+        <v>589</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>287</v>
+        <v>590</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -12022,10 +11994,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>559</v>
+        <v>591</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>559</v>
+        <v>591</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12045,23 +12017,19 @@
         <v>83</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>108</v>
+        <v>585</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>339</v>
+        <v>592</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>83</v>
       </c>
@@ -12109,7 +12077,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>343</v>
+        <v>591</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12118,7 +12086,7 @@
         <v>94</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>83</v>
+        <v>588</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>106</v>
@@ -12130,10 +12098,10 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>344</v>
+        <v>589</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>345</v>
+        <v>594</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -12144,10 +12112,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>560</v>
+        <v>595</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>560</v>
+        <v>595</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12170,18 +12138,20 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>561</v>
+        <v>263</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>562</v>
+        <v>596</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>563</v>
+        <v>597</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>598</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>599</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
       </c>
@@ -12205,13 +12175,13 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>83</v>
+        <v>178</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>83</v>
+        <v>600</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>83</v>
+        <v>601</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12229,7 +12199,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>560</v>
+        <v>595</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12247,27 +12217,27 @@
         <v>83</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>565</v>
+        <v>602</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>566</v>
+        <v>603</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>567</v>
+        <v>522</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>568</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>569</v>
+        <v>604</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>569</v>
+        <v>604</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12278,7 +12248,7 @@
         <v>81</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>83</v>
@@ -12290,18 +12260,20 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>570</v>
+        <v>263</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>571</v>
+        <v>605</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>572</v>
+        <v>606</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>608</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
       </c>
@@ -12325,13 +12297,13 @@
         <v>83</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>83</v>
+        <v>609</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>83</v>
+        <v>610</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>83</v>
@@ -12349,13 +12321,13 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>569</v>
+        <v>604</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>83</v>
@@ -12367,27 +12339,27 @@
         <v>83</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>574</v>
+        <v>602</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>576</v>
+        <v>522</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>577</v>
+        <v>83</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>578</v>
+        <v>611</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>578</v>
+        <v>611</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12398,7 +12370,7 @@
         <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>83</v>
@@ -12410,19 +12382,17 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>579</v>
+        <v>612</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>580</v>
+        <v>613</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>582</v>
-      </c>
+        <v>614</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>583</v>
+        <v>615</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12471,19 +12441,19 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>578</v>
+        <v>611</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>584</v>
+        <v>106</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>83</v>
@@ -12492,10 +12462,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>585</v>
+        <v>83</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>586</v>
+        <v>616</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12506,10 +12476,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>587</v>
+        <v>617</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>587</v>
+        <v>617</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12535,10 +12505,10 @@
         <v>108</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>109</v>
+        <v>618</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>110</v>
+        <v>619</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12589,7 +12559,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>111</v>
+        <v>617</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12601,7 +12571,7 @@
         <v>83</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>83</v>
@@ -12610,10 +12580,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>83</v>
+        <v>589</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>112</v>
+        <v>620</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12624,14 +12594,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>588</v>
+        <v>621</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>588</v>
+        <v>621</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12647,19 +12617,19 @@
         <v>83</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>115</v>
+        <v>622</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>116</v>
+        <v>623</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>117</v>
+        <v>624</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>118</v>
+        <v>625</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12709,7 +12679,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>122</v>
+        <v>621</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12721,7 +12691,7 @@
         <v>83</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>83</v>
@@ -12730,10 +12700,10 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>83</v>
+        <v>626</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>112</v>
+        <v>627</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12744,14 +12714,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>589</v>
+        <v>628</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>589</v>
+        <v>628</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>590</v>
+        <v>83</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12764,26 +12734,24 @@
         <v>83</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J86" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>115</v>
+        <v>629</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>591</v>
+        <v>630</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>592</v>
+        <v>631</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>83</v>
       </c>
@@ -12831,7 +12799,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>593</v>
+        <v>628</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12843,7 +12811,7 @@
         <v>83</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>83</v>
@@ -12852,10 +12820,10 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>83</v>
+        <v>626</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>197</v>
+        <v>633</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12866,10 +12834,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>594</v>
+        <v>634</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>594</v>
+        <v>634</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12880,28 +12848,32 @@
         <v>81</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>596</v>
+        <v>635</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>635</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>637</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
       </c>
@@ -12949,19 +12921,19 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>594</v>
+        <v>634</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>598</v>
+        <v>83</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>106</v>
+        <v>638</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>83</v>
@@ -12970,10 +12942,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>599</v>
+        <v>639</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>600</v>
+        <v>640</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12984,10 +12956,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>601</v>
+        <v>641</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>601</v>
+        <v>641</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13010,13 +12982,13 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>595</v>
+        <v>108</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>602</v>
+        <v>109</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>603</v>
+        <v>110</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13067,7 +13039,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>601</v>
+        <v>111</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13076,10 +13048,10 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>598</v>
+        <v>83</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>83</v>
@@ -13088,10 +13060,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>599</v>
+        <v>83</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>604</v>
+        <v>112</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -13102,21 +13074,21 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>605</v>
+        <v>642</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>605</v>
+        <v>642</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>83</v>
@@ -13128,20 +13100,18 @@
         <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>263</v>
+        <v>115</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>606</v>
+        <v>116</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>607</v>
+        <v>117</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>609</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>83</v>
       </c>
@@ -13165,13 +13135,13 @@
         <v>83</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>178</v>
+        <v>83</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>610</v>
+        <v>83</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>611</v>
+        <v>83</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>83</v>
@@ -13189,31 +13159,31 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>605</v>
+        <v>122</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>612</v>
+        <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>613</v>
+        <v>83</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>522</v>
+        <v>112</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -13224,14 +13194,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>614</v>
+        <v>643</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>614</v>
+        <v>643</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>83</v>
+        <v>580</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13244,25 +13214,25 @@
         <v>83</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>263</v>
+        <v>115</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>615</v>
+        <v>581</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>616</v>
+        <v>582</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>617</v>
+        <v>118</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>618</v>
+        <v>221</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13287,13 +13257,13 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>619</v>
+        <v>83</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>620</v>
+        <v>83</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13311,7 +13281,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>614</v>
+        <v>583</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13323,19 +13293,19 @@
         <v>83</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>612</v>
+        <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>613</v>
+        <v>83</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>522</v>
+        <v>197</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13346,10 +13316,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>621</v>
+        <v>644</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>621</v>
+        <v>644</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13357,32 +13327,34 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>622</v>
+        <v>263</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>623</v>
+        <v>645</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>646</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>647</v>
+      </c>
       <c r="O91" t="s" s="2">
-        <v>625</v>
+        <v>648</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13407,13 +13379,13 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>83</v>
+        <v>352</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>83</v>
+        <v>353</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13431,10 +13403,10 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>621</v>
+        <v>644</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>94</v>
@@ -13449,16 +13421,16 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>83</v>
+        <v>649</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>83</v>
+        <v>356</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>626</v>
+        <v>357</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>83</v>
+        <v>358</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>83</v>
@@ -13466,10 +13438,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>627</v>
+        <v>650</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>627</v>
+        <v>650</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13483,25 +13455,29 @@
         <v>94</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>108</v>
+        <v>651</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>628</v>
+        <v>652</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+        <v>653</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
       </c>
@@ -13525,13 +13501,13 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>83</v>
+        <v>655</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>83</v>
+        <v>656</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -13549,7 +13525,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>627</v>
+        <v>650</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13558,7 +13534,7 @@
         <v>94</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>83</v>
+        <v>657</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>106</v>
@@ -13567,27 +13543,27 @@
         <v>83</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>83</v>
+        <v>658</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>599</v>
+        <v>448</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>630</v>
+        <v>449</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>83</v>
+        <v>450</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>631</v>
+        <v>659</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>631</v>
+        <v>659</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13598,30 +13574,32 @@
         <v>81</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>632</v>
+        <v>263</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>633</v>
+        <v>660</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>634</v>
+        <v>661</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>662</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>507</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
       </c>
@@ -13645,13 +13623,13 @@
         <v>83</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>83</v>
+        <v>508</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>83</v>
+        <v>509</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
@@ -13669,16 +13647,16 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>631</v>
+        <v>659</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>83</v>
+        <v>663</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>106</v>
@@ -13690,10 +13668,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>636</v>
+        <v>197</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>637</v>
+        <v>511</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13704,14 +13682,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>638</v>
+        <v>664</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>638</v>
+        <v>664</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>83</v>
+        <v>513</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13727,21 +13705,23 @@
         <v>83</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>639</v>
+        <v>263</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>640</v>
+        <v>514</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>641</v>
+        <v>515</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="O94" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
       </c>
@@ -13765,13 +13745,13 @@
         <v>83</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>83</v>
+        <v>518</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>83</v>
+        <v>519</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -13789,7 +13769,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>638</v>
+        <v>664</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13807,27 +13787,27 @@
         <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>83</v>
+        <v>520</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>636</v>
+        <v>521</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>643</v>
+        <v>522</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>83</v>
+        <v>523</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>644</v>
+        <v>665</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>644</v>
+        <v>665</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13841,28 +13821,28 @@
         <v>82</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>579</v>
+        <v>84</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>645</v>
+        <v>666</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>645</v>
+        <v>667</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>646</v>
+        <v>572</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>647</v>
+        <v>573</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13911,7 +13891,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>644</v>
+        <v>665</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13923,7 +13903,7 @@
         <v>83</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>648</v>
+        <v>106</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>83</v>
@@ -13932,990 +13912,20 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>649</v>
+        <v>575</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>650</v>
+        <v>576</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="O97" s="2"/>
-      <c r="P97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="P99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="100" hidden="true">
-      <c r="A100" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="P100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="101" hidden="true">
-      <c r="A101" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="P101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="P102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="103" hidden="true">
-      <c r="A103" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="P103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP103" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP103">
+  <autoFilter ref="A1:AP95">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14925,7 +13935,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI102">
+  <conditionalFormatting sqref="A2:AI94">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -691,7 +691,7 @@
     <t>supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {workflow-supportingInfo|5.2.0}
+    <t xml:space="preserve">Extension {workflow-supportingInfo|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -4970,7 +4970,7 @@
         <v>82</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>123</v>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
